--- a/backend/data/jp_nagar/users.xlsx
+++ b/backend/data/jp_nagar/users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="71">
   <si>
     <t>User ID</t>
   </si>
@@ -67,46 +67,49 @@
     <t>c2ce62e5-d5f1-470c-b36f-4a8a7071cc68</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>All Centers</t>
+  </si>
+  <si>
+    <t>superadmin</t>
+  </si>
+  <si>
+    <t>$2a$10$tqobxN9F0XGe4VTvFWNkoOSs.mi7DAPlwatLyuRMwOMWaXH2vKgES</t>
+  </si>
+  <si>
+    <t>Central Super Admin</t>
+  </si>
+  <si>
+    <t>padmini.s@erafoundationindia.org</t>
+  </si>
+  <si>
+    <t>super_admin</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>9032f535-5325-4b07-9d75-67d2b5a31630</t>
+  </si>
+  <si>
     <t>jp_nagar</t>
   </si>
   <si>
     <t>J P Nagar, Bengaluru</t>
   </si>
   <si>
-    <t>superadmin</t>
-  </si>
-  <si>
-    <t>$2a$10$EAPPJic.YzM5j2Ze/.LoxueGqjFj0in5qQlVh9Ai0KN7GEUpu5cRi</t>
-  </si>
-  <si>
-    <t>Central Super Admin</t>
-  </si>
-  <si>
-    <t>superadmin@cims.edu</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>super_admin</t>
-  </si>
-  <si>
-    <t>manual</t>
-  </si>
-  <si>
-    <t>9032f535-5325-4b07-9d75-67d2b5a31630</t>
-  </si>
-  <si>
     <t>jp_nagar_admin</t>
   </si>
   <si>
-    <t>$2a$10$.2Pe/lrwo6a3pO9OsXHHTexjXOKUp788xmc.YzajshCrFoEPSQjza</t>
-  </si>
-  <si>
-    <t>J P Nagar, Bengaluru Admin</t>
-  </si>
-  <si>
-    <t>jp_nagar@cims.edu</t>
+    <t>$2a$10$DYbo/XfV3X50fW4Zy6iIm.G9U8ro/NvoT/3hJ0dEjeHt7SztxeTAa</t>
+  </si>
+  <si>
+    <t>Nayan G Achar</t>
+  </si>
+  <si>
+    <t>nayan.g@erafoundationindia.org</t>
   </si>
   <si>
     <t>admin</t>
@@ -128,6 +131,99 @@
   </si>
   <si>
     <t>student</t>
+  </si>
+  <si>
+    <t>4f082759-0788-40ca-ad7b-ea6a9eecafe6</t>
+  </si>
+  <si>
+    <t>guru</t>
+  </si>
+  <si>
+    <t>$2a$10$X4EaxZc4J6Gz.ZwiRLC2Zu1D8A8D3d7kwWh0lFp/6kAv9ghgm9mWW</t>
+  </si>
+  <si>
+    <t>Gururaj</t>
+  </si>
+  <si>
+    <t>gurubadiger367@gmail.com</t>
+  </si>
+  <si>
+    <t>7483311723</t>
+  </si>
+  <si>
+    <t>Comedkares</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>2745462b-5256-4302-a66e-5784b94af7ae</t>
+  </si>
+  <si>
+    <t>dhavalya</t>
+  </si>
+  <si>
+    <t>$2a$10$N7Fndd/PMzYNzqvKiGyW3O38TiAq7/6sshU7r.5ok548vZzhUUU12</t>
+  </si>
+  <si>
+    <t>Dhavalya Shree.T</t>
+  </si>
+  <si>
+    <t>dhavalyashreet@gmail.com</t>
+  </si>
+  <si>
+    <t>6363362268</t>
+  </si>
+  <si>
+    <t>9448482622</t>
+  </si>
+  <si>
+    <t>T John Institute of Technology</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>B.E</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>dab62990-e2ec-4762-8015-e05e1d21e0e5</t>
+  </si>
+  <si>
+    <t>Pragathi</t>
+  </si>
+  <si>
+    <t>$2a$10$P.jf2d.qWqIBWLWQDwZVYOKs0hBPev.43i/pNrQRf0mtxF7mICHN.</t>
+  </si>
+  <si>
+    <t>Pragathi Kanthayya Kanthimath</t>
+  </si>
+  <si>
+    <t>pragathi.k222@gmail.com</t>
+  </si>
+  <si>
+    <t>9035683821</t>
+  </si>
+  <si>
+    <t>9538916722</t>
+  </si>
+  <si>
+    <t>T JOHN INSTITUTE OF TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>ISE</t>
   </si>
 </sst>
 </file>
@@ -553,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -648,25 +744,25 @@
         <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="O2" s="2" t="b">
         <v>1</v>
@@ -675,51 +771,51 @@
         <v>46118.43890851852</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="4" t="b">
         <v>1</v>
@@ -728,51 +824,51 @@
         <v>46118.43890920139</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="2" t="b">
         <v>1</v>
@@ -781,11 +877,170 @@
         <v>46118.43890988426</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3">
+        <v>46123.28978731482</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
+        <v>46158.239801828706</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
+        <v>46158.240448819444</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>